--- a/excel-files/PASAY/MARCELA MARCELO ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/PASAY/MARCELA MARCELO ELEMENTARY SCHOOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF797F98-2E29-48E1-80F8-6B9AAA894175}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE6FD9E6-AA51-4D6E-8F35-DA6B8F79B592}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2932,8 +2932,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H97" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
-  <autoFilter ref="A1:H97" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H49" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+  <autoFilter ref="A1:H49" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
     <tableColumn id="2" xr3:uid="{56826189-DC15-4CA2-B5A0-8F4CEC09DDAB}" name="SUBJECTS"/>
@@ -2949,8 +2949,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA63" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
-  <autoFilter ref="A2:AA63" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA61" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+  <autoFilter ref="A2:AA61" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
     <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="55"/>
@@ -3005,8 +3005,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA83" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
-  <autoFilter ref="A2:AA83" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA65" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+  <autoFilter ref="A2:AA65" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
     <tableColumn id="2" xr3:uid="{73AEA048-228E-40E8-B07A-3A7C30BA0DC7}" name="SUBJECTS" dataDxfId="25"/>
@@ -4313,16 +4313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-    </row>
+    <row r="50" spans="1:8" ht="27.75" customHeight="1"/>
     <row r="51" spans="1:8" ht="15"/>
     <row r="52" spans="1:8" ht="15"/>
     <row r="53" spans="1:8" ht="15"/>
@@ -4373,8 +4364,8 @@
     <row r="98" ht="15"/>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C1:E50" name="Textbooks"/>
-    <protectedRange sqref="F1:F11 F13:F50" name="SOURCE"/>
+    <protectedRange sqref="C1:E49" name="Textbooks"/>
+    <protectedRange sqref="F1:F11 F13:F49" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
@@ -4394,7 +4385,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA112"/>
+  <dimension ref="A1:AA110"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -8276,31 +8267,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
-      <c r="J62" s="10"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="10"/>
-      <c r="O62" s="10"/>
-      <c r="P62" s="10"/>
-      <c r="S62" s="5"/>
-      <c r="T62" s="10"/>
-      <c r="U62" s="10"/>
-      <c r="V62" s="10"/>
-      <c r="Y62" s="5"/>
-      <c r="Z62" s="10"/>
-      <c r="AA62" s="10"/>
-    </row>
-    <row r="63" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
-      <c r="J63" s="10"/>
-      <c r="N63" s="10"/>
-      <c r="O63" s="10"/>
-      <c r="P63" s="10"/>
-      <c r="T63" s="10"/>
-      <c r="U63" s="10"/>
-      <c r="V63" s="10"/>
-      <c r="Z63" s="10"/>
-      <c r="AA63" s="10"/>
-    </row>
+    <row r="62" spans="1:27" ht="15"/>
+    <row r="63" spans="1:27" ht="15"/>
     <row r="64" spans="1:27" ht="15"/>
     <row r="65" ht="15"/>
     <row r="66" ht="15"/>
@@ -8317,14 +8285,12 @@
     <row r="77" ht="15"/>
     <row r="78" ht="15"/>
     <row r="79" ht="15"/>
-    <row r="80" ht="15"/>
-    <row r="81" ht="15"/>
-    <row r="112" ht="15"/>
+    <row r="110" ht="15"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 H33:I41 H43:I51 H53:I61 N13:P63 P2:R2 V2:X3 T13:V63 J6:J63 N4:P4 T4:V4 J4 N3:R3 Y13 Z4:AA63 H14:I21 H23:I31 H6:I12 D5:F12 D14:F21 D23:F31 D33:F41 D43:F51 D53:F61 K6:L12 K14:L21 K23:L31 K33:L41 K43:L51 K53:L61 N5:R12 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 T5:X12 W14:X21 W23:X31 W33:X41 W43:X51 W53:X61" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G23:G31 G33:G41 G43:G51 S4:S62 G5:G12 M5:M12 M14:M62 Y5:Y12 G14:G21 Y14:Y62 M3 G53:G61" name="SOURCE"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 H33:I41 H43:I51 H53:I61 Z4:AA61 P2:R2 V2:X3 J6:J61 T13:V61 N4:P4 T4:V4 J4 N3:R3 Y13 N13:P61 H14:I21 H23:I31 H6:I12 D5:F12 D14:F21 D23:F31 D33:F41 D43:F51 D53:F61 K6:L12 K14:L21 K23:L31 K33:L41 K43:L51 K53:L61 N5:R12 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 T5:X12 W14:X21 W23:X31 W33:X41 W43:X51 W53:X61" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G23:G31 G33:G41 G43:G51 M14:M61 G5:G12 M5:M12 Y14:Y61 Y5:Y12 G14:G21 G53:G61 M3 S4:S61" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -8333,18 +8299,12 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X53:X61" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X53:X61 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M62 Y14:Y62 S4:S62 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M61 Y14:Y61 S4:S61 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61" xr:uid="{E2C9A8F0-0B35-4AF4-AFAB-14FCBBFDF09E}">
-      <formula1>"2024,2025,2026"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51" xr:uid="{E6B6D01A-F89B-458A-995A-55159117FD83}">
-      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12512,496 +12472,121 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:28" s="7" customFormat="1"/>
-    <row r="67" spans="1:28" s="7" customFormat="1"/>
-    <row r="68" spans="1:28">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="7"/>
-      <c r="K68" s="7"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
-      <c r="N68" s="7"/>
-      <c r="O68" s="7"/>
-      <c r="P68" s="7"/>
-      <c r="Q68" s="7"/>
-      <c r="R68" s="7"/>
-      <c r="S68" s="7"/>
-      <c r="T68" s="7"/>
-      <c r="U68" s="7"/>
-      <c r="V68" s="7"/>
-      <c r="W68" s="7"/>
-      <c r="X68" s="7"/>
-      <c r="Y68" s="7"/>
-      <c r="Z68" s="7"/>
-      <c r="AA68" s="7"/>
+    <row r="66" spans="1:28" s="7" customFormat="1" ht="15">
+      <c r="A66"/>
+      <c r="B66"/>
+      <c r="C66"/>
+      <c r="D66"/>
+      <c r="E66"/>
+      <c r="F66"/>
+      <c r="G66"/>
+      <c r="H66"/>
+      <c r="I66"/>
+      <c r="J66"/>
+      <c r="K66"/>
+      <c r="L66"/>
+      <c r="M66"/>
+      <c r="N66"/>
+      <c r="O66"/>
+      <c r="P66"/>
+      <c r="Q66"/>
+      <c r="R66"/>
+      <c r="S66"/>
+      <c r="T66"/>
+      <c r="U66"/>
+      <c r="V66"/>
+      <c r="W66"/>
+      <c r="X66"/>
+      <c r="Y66"/>
+      <c r="Z66"/>
+      <c r="AA66"/>
+    </row>
+    <row r="67" spans="1:28" s="7" customFormat="1" ht="15">
+      <c r="A67"/>
+      <c r="B67"/>
+      <c r="C67"/>
+      <c r="D67"/>
+      <c r="E67"/>
+      <c r="F67"/>
+      <c r="G67"/>
+      <c r="H67"/>
+      <c r="I67"/>
+      <c r="J67"/>
+      <c r="K67"/>
+      <c r="L67"/>
+      <c r="M67"/>
+      <c r="N67"/>
+      <c r="O67"/>
+      <c r="P67"/>
+      <c r="Q67"/>
+      <c r="R67"/>
+      <c r="S67"/>
+      <c r="T67"/>
+      <c r="U67"/>
+      <c r="V67"/>
+      <c r="W67"/>
+      <c r="X67"/>
+      <c r="Y67"/>
+      <c r="Z67"/>
+      <c r="AA67"/>
+    </row>
+    <row r="68" spans="1:28" ht="15">
       <c r="AB68" s="7"/>
     </row>
-    <row r="69" spans="1:28">
-      <c r="A69" s="7"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="7"/>
-      <c r="K69" s="7"/>
-      <c r="L69" s="7"/>
-      <c r="M69" s="7"/>
-      <c r="N69" s="7"/>
-      <c r="O69" s="7"/>
-      <c r="P69" s="7"/>
-      <c r="Q69" s="7"/>
-      <c r="R69" s="7"/>
-      <c r="S69" s="7"/>
-      <c r="T69" s="7"/>
-      <c r="U69" s="7"/>
-      <c r="V69" s="7"/>
-      <c r="W69" s="7"/>
-      <c r="X69" s="7"/>
-      <c r="Y69" s="7"/>
-      <c r="Z69" s="7"/>
-      <c r="AA69" s="7"/>
+    <row r="69" spans="1:28" ht="15">
       <c r="AB69" s="7"/>
     </row>
-    <row r="70" spans="1:28">
-      <c r="A70" s="7"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7"/>
-      <c r="J70" s="7"/>
-      <c r="K70" s="7"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="7"/>
-      <c r="N70" s="7"/>
-      <c r="O70" s="7"/>
-      <c r="P70" s="7"/>
-      <c r="Q70" s="7"/>
-      <c r="R70" s="7"/>
-      <c r="S70" s="7"/>
-      <c r="T70" s="7"/>
-      <c r="U70" s="7"/>
-      <c r="V70" s="7"/>
-      <c r="W70" s="7"/>
-      <c r="X70" s="7"/>
-      <c r="Y70" s="7"/>
-      <c r="Z70" s="7"/>
-      <c r="AA70" s="7"/>
+    <row r="70" spans="1:28" ht="15">
       <c r="AB70" s="7"/>
     </row>
-    <row r="71" spans="1:28">
-      <c r="A71" s="7"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7"/>
-      <c r="J71" s="7"/>
-      <c r="K71" s="7"/>
-      <c r="L71" s="7"/>
-      <c r="M71" s="7"/>
-      <c r="N71" s="7"/>
-      <c r="O71" s="7"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="7"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="7"/>
-      <c r="T71" s="7"/>
-      <c r="U71" s="7"/>
-      <c r="V71" s="7"/>
-      <c r="W71" s="7"/>
-      <c r="X71" s="7"/>
-      <c r="Y71" s="7"/>
-      <c r="Z71" s="7"/>
-      <c r="AA71" s="7"/>
+    <row r="71" spans="1:28" ht="15">
       <c r="AB71" s="7"/>
     </row>
-    <row r="72" spans="1:28">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="7"/>
-      <c r="J72" s="7"/>
-      <c r="K72" s="7"/>
-      <c r="L72" s="7"/>
-      <c r="M72" s="7"/>
-      <c r="N72" s="7"/>
-      <c r="O72" s="7"/>
-      <c r="P72" s="7"/>
-      <c r="Q72" s="7"/>
-      <c r="R72" s="7"/>
-      <c r="S72" s="7"/>
-      <c r="T72" s="7"/>
-      <c r="U72" s="7"/>
-      <c r="V72" s="7"/>
-      <c r="W72" s="7"/>
-      <c r="X72" s="7"/>
-      <c r="Y72" s="7"/>
-      <c r="Z72" s="7"/>
-      <c r="AA72" s="7"/>
+    <row r="72" spans="1:28" ht="15">
       <c r="AB72" s="7"/>
     </row>
-    <row r="73" spans="1:28">
-      <c r="A73" s="7"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="7"/>
-      <c r="J73" s="7"/>
-      <c r="K73" s="7"/>
-      <c r="L73" s="7"/>
-      <c r="M73" s="7"/>
-      <c r="N73" s="7"/>
-      <c r="O73" s="7"/>
-      <c r="P73" s="7"/>
-      <c r="Q73" s="7"/>
-      <c r="R73" s="7"/>
-      <c r="S73" s="7"/>
-      <c r="T73" s="7"/>
-      <c r="U73" s="7"/>
-      <c r="V73" s="7"/>
-      <c r="W73" s="7"/>
-      <c r="X73" s="7"/>
-      <c r="Y73" s="7"/>
-      <c r="Z73" s="7"/>
-      <c r="AA73" s="7"/>
+    <row r="73" spans="1:28" ht="15">
       <c r="AB73" s="7"/>
     </row>
-    <row r="74" spans="1:28">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
-      <c r="P74" s="7"/>
-      <c r="Q74" s="7"/>
-      <c r="R74" s="7"/>
-      <c r="S74" s="7"/>
-      <c r="T74" s="7"/>
-      <c r="U74" s="7"/>
-      <c r="V74" s="7"/>
-      <c r="W74" s="7"/>
-      <c r="X74" s="7"/>
-      <c r="Y74" s="7"/>
-      <c r="Z74" s="7"/>
-      <c r="AA74" s="7"/>
+    <row r="74" spans="1:28" ht="15">
       <c r="AB74" s="7"/>
     </row>
-    <row r="75" spans="1:28">
-      <c r="A75" s="7"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
-      <c r="J75" s="7"/>
-      <c r="K75" s="7"/>
-      <c r="L75" s="7"/>
-      <c r="M75" s="7"/>
-      <c r="N75" s="7"/>
-      <c r="O75" s="7"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="7"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="7"/>
-      <c r="T75" s="7"/>
-      <c r="U75" s="7"/>
-      <c r="V75" s="7"/>
-      <c r="W75" s="7"/>
-      <c r="X75" s="7"/>
-      <c r="Y75" s="7"/>
-      <c r="Z75" s="7"/>
-      <c r="AA75" s="7"/>
+    <row r="75" spans="1:28" ht="15">
       <c r="AB75" s="7"/>
     </row>
-    <row r="76" spans="1:28">
-      <c r="A76" s="7"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
-      <c r="M76" s="7"/>
-      <c r="N76" s="7"/>
-      <c r="O76" s="7"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="7"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="7"/>
-      <c r="T76" s="7"/>
-      <c r="U76" s="7"/>
-      <c r="V76" s="7"/>
-      <c r="W76" s="7"/>
-      <c r="X76" s="7"/>
-      <c r="Y76" s="7"/>
-      <c r="Z76" s="7"/>
-      <c r="AA76" s="7"/>
+    <row r="76" spans="1:28" ht="15">
       <c r="AB76" s="7"/>
     </row>
-    <row r="77" spans="1:28">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-      <c r="I77" s="7"/>
-      <c r="J77" s="7"/>
-      <c r="K77" s="7"/>
-      <c r="L77" s="7"/>
-      <c r="M77" s="7"/>
-      <c r="N77" s="7"/>
-      <c r="O77" s="7"/>
-      <c r="P77" s="7"/>
-      <c r="Q77" s="7"/>
-      <c r="R77" s="7"/>
-      <c r="S77" s="7"/>
-      <c r="T77" s="7"/>
-      <c r="U77" s="7"/>
-      <c r="V77" s="7"/>
-      <c r="W77" s="7"/>
-      <c r="X77" s="7"/>
-      <c r="Y77" s="7"/>
-      <c r="Z77" s="7"/>
-      <c r="AA77" s="7"/>
+    <row r="77" spans="1:28" ht="15">
       <c r="AB77" s="7"/>
     </row>
-    <row r="78" spans="1:28">
-      <c r="A78" s="7"/>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
-      <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
-      <c r="I78" s="7"/>
-      <c r="J78" s="7"/>
-      <c r="K78" s="7"/>
-      <c r="L78" s="7"/>
-      <c r="M78" s="7"/>
-      <c r="N78" s="7"/>
-      <c r="O78" s="7"/>
-      <c r="P78" s="7"/>
-      <c r="Q78" s="7"/>
-      <c r="R78" s="7"/>
-      <c r="S78" s="7"/>
-      <c r="T78" s="7"/>
-      <c r="U78" s="7"/>
-      <c r="V78" s="7"/>
-      <c r="W78" s="7"/>
-      <c r="X78" s="7"/>
-      <c r="Y78" s="7"/>
-      <c r="Z78" s="7"/>
-      <c r="AA78" s="7"/>
+    <row r="78" spans="1:28" ht="15">
       <c r="AB78" s="7"/>
     </row>
-    <row r="79" spans="1:28">
-      <c r="A79" s="7"/>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
-      <c r="I79" s="7"/>
-      <c r="J79" s="7"/>
-      <c r="K79" s="7"/>
-      <c r="L79" s="7"/>
-      <c r="M79" s="7"/>
-      <c r="N79" s="7"/>
-      <c r="O79" s="7"/>
-      <c r="P79" s="7"/>
-      <c r="Q79" s="7"/>
-      <c r="R79" s="7"/>
-      <c r="S79" s="7"/>
-      <c r="T79" s="7"/>
-      <c r="U79" s="7"/>
-      <c r="V79" s="7"/>
-      <c r="W79" s="7"/>
-      <c r="X79" s="7"/>
-      <c r="Y79" s="7"/>
-      <c r="Z79" s="7"/>
-      <c r="AA79" s="7"/>
+    <row r="79" spans="1:28" ht="15">
       <c r="AB79" s="7"/>
     </row>
-    <row r="80" spans="1:28">
-      <c r="A80" s="7"/>
-      <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-      <c r="I80" s="7"/>
-      <c r="J80" s="7"/>
-      <c r="K80" s="7"/>
-      <c r="L80" s="7"/>
-      <c r="M80" s="7"/>
-      <c r="N80" s="7"/>
-      <c r="O80" s="7"/>
-      <c r="P80" s="7"/>
-      <c r="Q80" s="7"/>
-      <c r="R80" s="7"/>
-      <c r="S80" s="7"/>
-      <c r="T80" s="7"/>
-      <c r="U80" s="7"/>
-      <c r="V80" s="7"/>
-      <c r="W80" s="7"/>
-      <c r="X80" s="7"/>
-      <c r="Y80" s="7"/>
-      <c r="Z80" s="7"/>
-      <c r="AA80" s="7"/>
+    <row r="80" spans="1:28" ht="15">
       <c r="AB80" s="7"/>
     </row>
-    <row r="81" spans="1:28">
-      <c r="A81" s="7"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
-      <c r="I81" s="7"/>
-      <c r="J81" s="7"/>
-      <c r="K81" s="7"/>
-      <c r="L81" s="7"/>
-      <c r="M81" s="7"/>
-      <c r="N81" s="7"/>
-      <c r="O81" s="7"/>
-      <c r="P81" s="7"/>
-      <c r="Q81" s="7"/>
-      <c r="R81" s="7"/>
-      <c r="S81" s="7"/>
-      <c r="T81" s="7"/>
-      <c r="U81" s="7"/>
-      <c r="V81" s="7"/>
-      <c r="W81" s="7"/>
-      <c r="X81" s="7"/>
-      <c r="Y81" s="7"/>
-      <c r="Z81" s="7"/>
-      <c r="AA81" s="7"/>
+    <row r="81" spans="28:28" ht="15">
       <c r="AB81" s="7"/>
     </row>
-    <row r="82" spans="1:28">
-      <c r="A82" s="7"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="G82" s="7"/>
-      <c r="H82" s="7"/>
-      <c r="I82" s="7"/>
-      <c r="J82" s="7"/>
-      <c r="K82" s="7"/>
-      <c r="L82" s="7"/>
-      <c r="M82" s="7"/>
-      <c r="N82" s="7"/>
-      <c r="O82" s="7"/>
-      <c r="P82" s="7"/>
-      <c r="Q82" s="7"/>
-      <c r="R82" s="7"/>
-      <c r="S82" s="7"/>
-      <c r="T82" s="7"/>
-      <c r="U82" s="7"/>
-      <c r="V82" s="7"/>
-      <c r="W82" s="7"/>
-      <c r="X82" s="7"/>
-      <c r="Y82" s="7"/>
-      <c r="Z82" s="7"/>
-      <c r="AA82" s="7"/>
+    <row r="82" spans="28:28" ht="15">
       <c r="AB82" s="7"/>
     </row>
-    <row r="83" spans="1:28">
-      <c r="A83" s="7"/>
-      <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
-      <c r="I83" s="7"/>
-      <c r="J83" s="7"/>
-      <c r="K83" s="7"/>
-      <c r="L83" s="7"/>
-      <c r="M83" s="7"/>
-      <c r="N83" s="7"/>
-      <c r="O83" s="7"/>
-      <c r="P83" s="7"/>
-      <c r="Q83" s="7"/>
-      <c r="R83" s="7"/>
-      <c r="S83" s="7"/>
-      <c r="T83" s="7"/>
-      <c r="U83" s="7"/>
-      <c r="V83" s="7"/>
-      <c r="W83" s="7"/>
-      <c r="X83" s="7"/>
-      <c r="Y83" s="7"/>
-      <c r="Z83" s="7"/>
-      <c r="AA83" s="7"/>
+    <row r="83" spans="28:28" ht="15">
       <c r="AB83" s="7"/>
     </row>
-    <row r="84" spans="1:28" ht="15"/>
-    <row r="85" spans="1:28" ht="15"/>
-    <row r="86" spans="1:28" ht="15"/>
-    <row r="87" spans="1:28" ht="15"/>
-    <row r="88" spans="1:28" ht="15"/>
-    <row r="89" spans="1:28" ht="15"/>
-    <row r="90" spans="1:28" ht="15"/>
-    <row r="91" spans="1:28" ht="15"/>
+    <row r="84" spans="28:28" ht="15"/>
+    <row r="85" spans="28:28" ht="15"/>
+    <row r="86" spans="28:28" ht="15"/>
+    <row r="87" spans="28:28" ht="15"/>
+    <row r="88" spans="28:28" ht="15"/>
+    <row r="89" spans="28:28" ht="15"/>
+    <row r="90" spans="28:28" ht="15"/>
+    <row r="91" spans="28:28" ht="15"/>
+    <row r="122" ht="15"/>
     <row r="140" ht="15"/>
   </sheetData>
   <protectedRanges>
@@ -13016,17 +12601,11 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X55:X65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025,2026"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65" xr:uid="{E95F1EA6-702E-4A8F-BB02-72B5BB31B72D}">
-      <formula1>"2024,2025,2026"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53" xr:uid="{624E31B2-FF9F-4B0E-B069-DB27B632797D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X55:X65 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
